--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/WYOMING_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/WYOMING_2023.xlsx
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C73">
